--- a/atletas_data.xlsx
+++ b/atletas_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2002F9A1-DD4A-4A82-8A9C-5C257657F414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE87E559-2A20-49DB-85A6-29C3CC7054EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,46 +146,46 @@
     <t>Alejandro Beltran</t>
   </si>
   <si>
-    <t>JG2025</t>
-  </si>
-  <si>
-    <t>CQ2025</t>
-  </si>
-  <si>
-    <t>LT2025</t>
-  </si>
-  <si>
-    <t>KV2025</t>
-  </si>
-  <si>
-    <t>LR2025</t>
-  </si>
-  <si>
-    <t>EG2025</t>
-  </si>
-  <si>
-    <t>NC2025</t>
-  </si>
-  <si>
-    <t>OT2025</t>
-  </si>
-  <si>
-    <t>TC2025</t>
-  </si>
-  <si>
-    <t>TO2025</t>
-  </si>
-  <si>
-    <t>GA2025</t>
-  </si>
-  <si>
-    <t>JS2025</t>
-  </si>
-  <si>
-    <t>AB2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">Atleta </t>
+  </si>
+  <si>
+    <t>JG1022963849</t>
+  </si>
+  <si>
+    <t>CQ79815328</t>
+  </si>
+  <si>
+    <t>LT1021677418</t>
+  </si>
+  <si>
+    <t>KV1000774725</t>
+  </si>
+  <si>
+    <t>LR1159713075</t>
+  </si>
+  <si>
+    <t>EG1023900647</t>
+  </si>
+  <si>
+    <t>NC1013121391</t>
+  </si>
+  <si>
+    <t>OT1010841874</t>
+  </si>
+  <si>
+    <t>TC1033793163</t>
+  </si>
+  <si>
+    <t>TO1019606649</t>
+  </si>
+  <si>
+    <t>GA1021398524</t>
+  </si>
+  <si>
+    <t>JS1016728407</t>
+  </si>
+  <si>
+    <t>AB1028784398</t>
   </si>
 </sst>
 </file>
@@ -566,7 +566,7 @@
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
     <col min="2" max="2" width="16.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="3" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -625,10 +625,10 @@
         <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3">
         <v>161</v>
@@ -651,10 +651,10 @@
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3">
         <v>161</v>
@@ -677,10 +677,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3">
         <v>81</v>
@@ -703,10 +703,10 @@
         <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E6" s="3">
         <v>156</v>
@@ -729,10 +729,10 @@
         <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3">
         <v>121</v>
@@ -755,10 +755,10 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3">
         <v>131</v>
@@ -781,10 +781,10 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E9" s="3">
         <v>121</v>
@@ -807,10 +807,10 @@
         <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E10" s="3">
         <v>106</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3">
         <v>91</v>
@@ -859,10 +859,10 @@
         <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E12" s="3">
         <v>86</v>
@@ -885,10 +885,10 @@
         <v>32</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E13" s="3">
         <v>101</v>
@@ -911,10 +911,10 @@
         <v>34</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E14" s="3">
         <v>76</v>
@@ -937,10 +937,10 @@
         <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E15" s="3">
         <v>101</v>

--- a/atletas_data.xlsx
+++ b/atletas_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE87E559-2A20-49DB-85A6-29C3CC7054EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02227179-47DD-48A9-AF31-FA61F6D75E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -186,6 +186,69 @@
   </si>
   <si>
     <t>AB1028784398</t>
+  </si>
+  <si>
+    <t>RUU-431</t>
+  </si>
+  <si>
+    <t>Cristofer Rivera</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>RUU-437</t>
+  </si>
+  <si>
+    <t>Diego Rojas</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>RUU-444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karen Rodriguez </t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>RUU-501</t>
+  </si>
+  <si>
+    <t>Davinse Alvarado</t>
+  </si>
+  <si>
+    <t>DA</t>
+  </si>
+  <si>
+    <t>RUU-502</t>
+  </si>
+  <si>
+    <t>Erick Sanchez</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>RUU-503</t>
+  </si>
+  <si>
+    <t>Sammy Tobar</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>RUU-504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angie Sanchez </t>
+  </si>
+  <si>
+    <t>AS</t>
   </si>
 </sst>
 </file>
@@ -561,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -956,10 +1019,103 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H17" s="2"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
